--- a/segmentation_tracker.xlsx
+++ b/segmentation_tracker.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Segmentation Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="rtorn patients" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1659,4 +1660,210 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sequence</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Filename</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>AC00AB71F1A762</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>SAG_PD_DRB_11</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>AC00AB71F1A762_SAG_PD_DRB_11.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>AC0100AFE1493E</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>SAG_PD_TSE_6</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>AC0100AFE1493E_SAG_PD_TSE_6.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>AC06729D928F6D</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>SAG_PD_TSE_12</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>AC06729D928F6D_SAG_PD_TSE_12.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>AC093D30C56ED7</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SAG_PD_TSE_6</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>AC093D30C56ED7_SAG_PD_TSE_6.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>AC0E9D7C7A2E8F</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>SAG_PD_TSE_7</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>AC0E9D7C7A2E8F_SAG_PD_TSE_7.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>AC116435D25299</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>SAG_PD_TSE_11</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>AC116435D25299_SAG_PD_TSE_11.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>AC13D01F99D88C</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>SAG_PD_TSE_5</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>AC13D01F99D88C_SAG_PD_TSE_5.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>AC152F0CF07CF3</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Sag_PD_FSE_7</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>AC152F0CF07CF3_Sag_PD_FSE_7.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>AC1A200F61EDC1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>SAG_PD_TSE_5</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>AC1A200F61EDC1_SAG_PD_TSE_5.nii.gz</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>AC1CEC4C14F850</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>SAG_PD_TSE_5001</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>AC1CEC4C14F850_SAG_PD_TSE_5001.nii.gz</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>